--- a/csv/error.xlsx
+++ b/csv/error.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2023_IPIN_Competition_Track03\csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2023_IPIN_Competition_Track03\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF152572-C9C5-4E3F-B14B-F218BF18C8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28740" windowHeight="11535"/>
+    <workbookView xWindow="8040" yWindow="924" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="24">
   <si>
     <t>RMSE</t>
   </si>
@@ -103,13 +104,21 @@
   </si>
   <si>
     <t>EKF(R1~R3)(wifi_lat,lon)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以上是舊的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這裡是新的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -127,12 +136,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -149,7 +164,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -158,6 +173,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,35 +459,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S43"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="L1" s="2" t="s">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="L1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -504,7 +525,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -545,7 +566,7 @@
         <v>3.6838000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -586,7 +607,7 @@
         <v>2.7338</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -627,7 +648,7 @@
         <v>2.4691000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -668,28 +689,28 @@
         <v>11.3207</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="L8" s="2" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="L8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
@@ -728,7 +749,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -769,7 +790,7 @@
         <v>3.6934</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -810,7 +831,7 @@
         <v>2.7913999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -851,7 +872,7 @@
         <v>2.4184999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -891,9 +912,955 @@
       <c r="O13">
         <v>11.230700000000001</v>
       </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="L15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" t="s">
+        <v>10</v>
+      </c>
+      <c r="N16" t="s">
+        <v>12</v>
+      </c>
+      <c r="O16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>9.1072000000000006</v>
+      </c>
+      <c r="C17">
+        <v>6.0353000000000003</v>
+      </c>
+      <c r="D17">
+        <v>6.7004000000000001</v>
+      </c>
+      <c r="E17">
+        <v>9.4867000000000008</v>
+      </c>
+      <c r="G17">
+        <v>4.1242000000000001</v>
+      </c>
+      <c r="H17">
+        <v>5.8876999999999997</v>
+      </c>
+      <c r="I17">
+        <v>4.9119999999999999</v>
+      </c>
+      <c r="J17">
+        <v>3.8946999999999998</v>
+      </c>
+      <c r="L17">
+        <v>5.3537999999999997</v>
+      </c>
+      <c r="M17">
+        <v>5.0678999999999998</v>
+      </c>
+      <c r="N17">
+        <v>5.0345000000000004</v>
+      </c>
+      <c r="O17">
+        <v>3.6934</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>7.242</v>
+      </c>
+      <c r="C18">
+        <v>5.3532000000000002</v>
+      </c>
+      <c r="D18">
+        <v>5.3358999999999996</v>
+      </c>
+      <c r="E18">
+        <v>7.8438999999999997</v>
+      </c>
+      <c r="G18">
+        <v>3.5434999999999999</v>
+      </c>
+      <c r="H18">
+        <v>4.7546999999999997</v>
+      </c>
+      <c r="I18">
+        <v>3.8967000000000001</v>
+      </c>
+      <c r="J18">
+        <v>2.7877000000000001</v>
+      </c>
+      <c r="L18">
+        <v>4.0968999999999998</v>
+      </c>
+      <c r="M18">
+        <v>4.1369999999999996</v>
+      </c>
+      <c r="N18">
+        <v>3.9899</v>
+      </c>
+      <c r="O18">
+        <v>2.7913999999999999</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>5.5221</v>
+      </c>
+      <c r="C19">
+        <v>2.7871999999999999</v>
+      </c>
+      <c r="D19">
+        <v>4.0525000000000002</v>
+      </c>
+      <c r="E19">
+        <v>5.3357999999999999</v>
+      </c>
+      <c r="G19">
+        <v>2.11</v>
+      </c>
+      <c r="H19">
+        <v>3.4725000000000001</v>
+      </c>
+      <c r="I19">
+        <v>2.9906000000000001</v>
+      </c>
+      <c r="J19">
+        <v>2.7198000000000002</v>
+      </c>
+      <c r="L19">
+        <v>3.4464999999999999</v>
+      </c>
+      <c r="M19">
+        <v>2.9272</v>
+      </c>
+      <c r="N19">
+        <v>3.0703999999999998</v>
+      </c>
+      <c r="O19">
+        <v>2.4184999999999999</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20">
+        <v>20.974299999999999</v>
+      </c>
+      <c r="C20">
+        <v>10.7125</v>
+      </c>
+      <c r="D20">
+        <v>16.854399999999998</v>
+      </c>
+      <c r="E20">
+        <v>22.290800000000001</v>
+      </c>
+      <c r="G20">
+        <v>8.0494000000000003</v>
+      </c>
+      <c r="H20">
+        <v>12.966699999999999</v>
+      </c>
+      <c r="I20">
+        <v>11.0602</v>
+      </c>
+      <c r="J20">
+        <v>13.286099999999999</v>
+      </c>
+      <c r="L20">
+        <v>17.970400000000001</v>
+      </c>
+      <c r="M20">
+        <v>10.7455</v>
+      </c>
+      <c r="N20">
+        <v>11.7196</v>
+      </c>
+      <c r="O20">
+        <v>11.230700000000001</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="22" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="L24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N25" t="s">
+        <v>12</v>
+      </c>
+      <c r="O25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26">
+        <v>10.033899999999999</v>
+      </c>
+      <c r="C26">
+        <v>6.0415000000000001</v>
+      </c>
+      <c r="D26">
+        <v>6.7534000000000001</v>
+      </c>
+      <c r="E26">
+        <v>10.2562</v>
+      </c>
+      <c r="G26">
+        <v>4.9885999999999999</v>
+      </c>
+      <c r="H26">
+        <v>7.8017000000000003</v>
+      </c>
+      <c r="I26">
+        <v>7.6212999999999997</v>
+      </c>
+      <c r="J26">
+        <v>5.0720999999999998</v>
+      </c>
+      <c r="L26">
+        <v>6.4157000000000002</v>
+      </c>
+      <c r="M26">
+        <v>7.3537999999999997</v>
+      </c>
+      <c r="N26">
+        <v>7.1028000000000002</v>
+      </c>
+      <c r="O26">
+        <v>5.4889000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>7.7969999999999997</v>
+      </c>
+      <c r="C27">
+        <v>5.2698999999999998</v>
+      </c>
+      <c r="D27">
+        <v>5.3097000000000003</v>
+      </c>
+      <c r="E27">
+        <v>8.2230000000000008</v>
+      </c>
+      <c r="G27">
+        <v>4.0590999999999999</v>
+      </c>
+      <c r="H27">
+        <v>6.2980999999999998</v>
+      </c>
+      <c r="I27">
+        <v>6.3018999999999998</v>
+      </c>
+      <c r="J27">
+        <v>3.5600999999999998</v>
+      </c>
+      <c r="L27">
+        <v>4.8029000000000002</v>
+      </c>
+      <c r="M27">
+        <v>6.0202999999999998</v>
+      </c>
+      <c r="N27">
+        <v>6.2112999999999996</v>
+      </c>
+      <c r="O27">
+        <v>3.6322999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>6.3155999999999999</v>
+      </c>
+      <c r="C28">
+        <v>2.9542999999999999</v>
+      </c>
+      <c r="D28">
+        <v>4.1733000000000002</v>
+      </c>
+      <c r="E28">
+        <v>6.1295999999999999</v>
+      </c>
+      <c r="G28">
+        <v>2.9</v>
+      </c>
+      <c r="H28">
+        <v>4.6043000000000003</v>
+      </c>
+      <c r="I28">
+        <v>4.2861000000000002</v>
+      </c>
+      <c r="J28">
+        <v>3.6126999999999998</v>
+      </c>
+      <c r="L28">
+        <v>4.2537000000000003</v>
+      </c>
+      <c r="M28">
+        <v>4.2229999999999999</v>
+      </c>
+      <c r="N28">
+        <v>3.4451999999999998</v>
+      </c>
+      <c r="O28">
+        <v>4.1151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29">
+        <v>21.332999999999998</v>
+      </c>
+      <c r="C29">
+        <v>10.309799999999999</v>
+      </c>
+      <c r="D29">
+        <v>17.6297</v>
+      </c>
+      <c r="E29">
+        <v>28.0839</v>
+      </c>
+      <c r="G29">
+        <v>14.8338</v>
+      </c>
+      <c r="H29">
+        <v>19.241299999999999</v>
+      </c>
+      <c r="I29">
+        <v>20.048400000000001</v>
+      </c>
+      <c r="J29">
+        <v>15.324299999999999</v>
+      </c>
+      <c r="L29">
+        <v>19.8002</v>
+      </c>
+      <c r="M29">
+        <v>17.828800000000001</v>
+      </c>
+      <c r="N29">
+        <v>12.6289</v>
+      </c>
+      <c r="O29">
+        <v>19.4252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="L31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33">
+        <v>9.1072000000000006</v>
+      </c>
+      <c r="C33">
+        <v>6.0353000000000003</v>
+      </c>
+      <c r="D33">
+        <v>6.7004000000000001</v>
+      </c>
+      <c r="E33">
+        <v>9.4867000000000008</v>
+      </c>
+      <c r="G33">
+        <v>5.1012000000000004</v>
+      </c>
+      <c r="H33">
+        <v>8.0045999999999999</v>
+      </c>
+      <c r="I33">
+        <v>7.6547999999999998</v>
+      </c>
+      <c r="J33">
+        <v>5.4198000000000004</v>
+      </c>
+      <c r="L33">
+        <v>5.8639000000000001</v>
+      </c>
+      <c r="M33">
+        <v>7.5293999999999999</v>
+      </c>
+      <c r="N33">
+        <v>7.1844000000000001</v>
+      </c>
+      <c r="O33">
+        <v>5.7424999999999997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>7.242</v>
+      </c>
+      <c r="C34">
+        <v>5.3532000000000002</v>
+      </c>
+      <c r="D34">
+        <v>5.3358999999999996</v>
+      </c>
+      <c r="E34">
+        <v>7.8438999999999997</v>
+      </c>
+      <c r="G34">
+        <v>4.0896999999999997</v>
+      </c>
+      <c r="H34">
+        <v>6.6719999999999997</v>
+      </c>
+      <c r="I34">
+        <v>6.3747999999999996</v>
+      </c>
+      <c r="J34">
+        <v>3.8736000000000002</v>
+      </c>
+      <c r="L34">
+        <v>4.6543000000000001</v>
+      </c>
+      <c r="M34">
+        <v>6.3353000000000002</v>
+      </c>
+      <c r="N34">
+        <v>6.3128000000000002</v>
+      </c>
+      <c r="O34">
+        <v>4.0186000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35">
+        <v>5.5221</v>
+      </c>
+      <c r="C35">
+        <v>2.7871999999999999</v>
+      </c>
+      <c r="D35">
+        <v>4.0525000000000002</v>
+      </c>
+      <c r="E35">
+        <v>5.3357999999999999</v>
+      </c>
+      <c r="G35">
+        <v>3.0491000000000001</v>
+      </c>
+      <c r="H35">
+        <v>4.4225000000000003</v>
+      </c>
+      <c r="I35">
+        <v>4.2375999999999996</v>
+      </c>
+      <c r="J35">
+        <v>3.7907999999999999</v>
+      </c>
+      <c r="L35">
+        <v>3.5669</v>
+      </c>
+      <c r="M35">
+        <v>4.0689000000000002</v>
+      </c>
+      <c r="N35">
+        <v>3.4298000000000002</v>
+      </c>
+      <c r="O35">
+        <v>4.1020000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>20.974299999999999</v>
+      </c>
+      <c r="C36">
+        <v>10.7125</v>
+      </c>
+      <c r="D36">
+        <v>16.854399999999998</v>
+      </c>
+      <c r="E36">
+        <v>22.290800000000001</v>
+      </c>
+      <c r="G36">
+        <v>14.8813</v>
+      </c>
+      <c r="H36">
+        <v>18.823499999999999</v>
+      </c>
+      <c r="I36">
+        <v>19.4801</v>
+      </c>
+      <c r="J36">
+        <v>16.401</v>
+      </c>
+      <c r="L36">
+        <v>14.622199999999999</v>
+      </c>
+      <c r="M36">
+        <v>17.456800000000001</v>
+      </c>
+      <c r="N36">
+        <v>12.3162</v>
+      </c>
+      <c r="O36">
+        <v>19.483000000000001</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="L38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
+        <v>8</v>
+      </c>
+      <c r="M39" t="s">
+        <v>10</v>
+      </c>
+      <c r="N39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40">
+        <v>9.1072000000000006</v>
+      </c>
+      <c r="C40">
+        <v>6.0353000000000003</v>
+      </c>
+      <c r="D40">
+        <v>6.7004000000000001</v>
+      </c>
+      <c r="E40">
+        <v>9.4867000000000008</v>
+      </c>
+      <c r="G40">
+        <v>5.1334999999999997</v>
+      </c>
+      <c r="H40">
+        <v>8.0663</v>
+      </c>
+      <c r="I40">
+        <v>7.6698000000000004</v>
+      </c>
+      <c r="J40">
+        <v>5.5716000000000001</v>
+      </c>
+      <c r="L40">
+        <v>5.9287000000000001</v>
+      </c>
+      <c r="M40">
+        <v>7.6289999999999996</v>
+      </c>
+      <c r="N40">
+        <v>7.1372</v>
+      </c>
+      <c r="O40">
+        <v>5.7450000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>7.242</v>
+      </c>
+      <c r="C41">
+        <v>5.3532000000000002</v>
+      </c>
+      <c r="D41">
+        <v>5.3358999999999996</v>
+      </c>
+      <c r="E41">
+        <v>7.8438999999999997</v>
+      </c>
+      <c r="G41">
+        <v>4.1433</v>
+      </c>
+      <c r="H41">
+        <v>6.7411000000000003</v>
+      </c>
+      <c r="I41">
+        <v>6.4127000000000001</v>
+      </c>
+      <c r="J41">
+        <v>3.9232</v>
+      </c>
+      <c r="L41">
+        <v>4.7436999999999996</v>
+      </c>
+      <c r="M41">
+        <v>6.4145000000000003</v>
+      </c>
+      <c r="N41">
+        <v>6.2775999999999996</v>
+      </c>
+      <c r="O41">
+        <v>3.9719000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42">
+        <v>5.5221</v>
+      </c>
+      <c r="C42">
+        <v>2.7871999999999999</v>
+      </c>
+      <c r="D42">
+        <v>4.0525000000000002</v>
+      </c>
+      <c r="E42">
+        <v>5.3357999999999999</v>
+      </c>
+      <c r="G42">
+        <v>3.0308999999999999</v>
+      </c>
+      <c r="H42">
+        <v>4.4298000000000002</v>
+      </c>
+      <c r="I42">
+        <v>4.2073999999999998</v>
+      </c>
+      <c r="J42">
+        <v>3.9561999999999999</v>
+      </c>
+      <c r="L42">
+        <v>3.5562</v>
+      </c>
+      <c r="M42">
+        <v>4.1299000000000001</v>
+      </c>
+      <c r="N42">
+        <v>3.3957000000000002</v>
+      </c>
+      <c r="O42">
+        <v>4.1506999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43">
+        <v>20.974299999999999</v>
+      </c>
+      <c r="C43">
+        <v>10.7125</v>
+      </c>
+      <c r="D43">
+        <v>16.854399999999998</v>
+      </c>
+      <c r="E43">
+        <v>22.290800000000001</v>
+      </c>
+      <c r="G43">
+        <v>14.5664</v>
+      </c>
+      <c r="H43">
+        <v>18.603300000000001</v>
+      </c>
+      <c r="I43">
+        <v>19.517900000000001</v>
+      </c>
+      <c r="J43">
+        <v>16.264099999999999</v>
+      </c>
+      <c r="L43">
+        <v>14.622199999999999</v>
+      </c>
+      <c r="M43">
+        <v>17.232099999999999</v>
+      </c>
+      <c r="N43">
+        <v>12.384399999999999</v>
+      </c>
+      <c r="O43">
+        <v>19.345099999999999</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="20">
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="L38:O38"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="L31:O31"/>
     <mergeCell ref="L1:O1"/>
     <mergeCell ref="L8:O8"/>
     <mergeCell ref="B1:E1"/>

--- a/csv/error.xlsx
+++ b/csv/error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2023_IPIN_Competition_Track03\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF152572-C9C5-4E3F-B14B-F218BF18C8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B055982-7ED1-4CD1-B517-9DCECC0955FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8040" yWindow="924" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="28">
   <si>
     <t>RMSE</t>
   </si>
@@ -112,6 +112,22 @@
   </si>
   <si>
     <t>這裡是新的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EKF(R1~R3)(fused_lat,lon)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EKF(R1~R4)(fused_lat,lon)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EKF(R1)(fused_lat,lon)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這裡是最新的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -164,7 +180,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -179,6 +195,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,32 +479,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="L1" s="3" t="s">
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="L1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
@@ -690,25 +709,25 @@
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="L8" s="3" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="L8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
@@ -922,25 +941,25 @@
       <c r="S14" s="2"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="L15" s="3" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="L15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
@@ -1159,33 +1178,33 @@
       <c r="O20">
         <v>11.230700000000001</v>
       </c>
-      <c r="Q20" s="3" t="s">
+      <c r="Q20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
     </row>
     <row r="22" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="L24" s="3" t="s">
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="L24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
@@ -1230,40 +1249,40 @@
         <v>0</v>
       </c>
       <c r="B26">
-        <v>10.033899999999999</v>
+        <v>12.9226334079941</v>
       </c>
       <c r="C26">
-        <v>6.0415000000000001</v>
+        <v>11.279463788733899</v>
       </c>
       <c r="D26">
-        <v>6.7534000000000001</v>
+        <v>8.3753137072889494</v>
       </c>
       <c r="E26">
-        <v>10.2562</v>
+        <v>20.414639302315098</v>
       </c>
       <c r="G26">
-        <v>4.9885999999999999</v>
+        <v>9.2443529216786295</v>
       </c>
       <c r="H26">
-        <v>7.8017000000000003</v>
+        <v>10.574718446765401</v>
       </c>
       <c r="I26">
-        <v>7.6212999999999997</v>
+        <v>7.9462428018564504</v>
       </c>
       <c r="J26">
-        <v>5.0720999999999998</v>
+        <v>12.2249696301109</v>
       </c>
       <c r="L26">
-        <v>6.4157000000000002</v>
+        <v>6.5592623721608803</v>
       </c>
       <c r="M26">
-        <v>7.3537999999999997</v>
+        <v>10.323050458630499</v>
       </c>
       <c r="N26">
-        <v>7.1028000000000002</v>
+        <v>8.3853775250676108</v>
       </c>
       <c r="O26">
-        <v>5.4889000000000001</v>
+        <v>8.68679227273614</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -1271,40 +1290,40 @@
         <v>2</v>
       </c>
       <c r="B27">
-        <v>7.7969999999999997</v>
+        <v>11.3374353772259</v>
       </c>
       <c r="C27">
-        <v>5.2698999999999998</v>
+        <v>8.6579712106884497</v>
       </c>
       <c r="D27">
-        <v>5.3097000000000003</v>
+        <v>6.89697399140291</v>
       </c>
       <c r="E27">
-        <v>8.2230000000000008</v>
+        <v>14.229091281558199</v>
       </c>
       <c r="G27">
-        <v>4.0590999999999999</v>
+        <v>5.6950683959134496</v>
       </c>
       <c r="H27">
-        <v>6.2980999999999998</v>
+        <v>8.1741985374592403</v>
       </c>
       <c r="I27">
-        <v>6.3018999999999998</v>
+        <v>6.4598301672712202</v>
       </c>
       <c r="J27">
-        <v>3.5600999999999998</v>
+        <v>5.8658887537840796</v>
       </c>
       <c r="L27">
-        <v>4.8029000000000002</v>
+        <v>5.2780716960474603</v>
       </c>
       <c r="M27">
-        <v>6.0202999999999998</v>
+        <v>7.8043058089816197</v>
       </c>
       <c r="N27">
-        <v>6.2112999999999996</v>
+        <v>6.72764767063821</v>
       </c>
       <c r="O27">
-        <v>3.6322999999999999</v>
+        <v>5.5623289478311397</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -1312,40 +1331,40 @@
         <v>4</v>
       </c>
       <c r="B28">
-        <v>6.3155999999999999</v>
+        <v>6.2013718856903397</v>
       </c>
       <c r="C28">
-        <v>2.9542999999999999</v>
+        <v>7.2295115932025702</v>
       </c>
       <c r="D28">
-        <v>4.1733000000000002</v>
+        <v>4.7515923075758497</v>
       </c>
       <c r="E28">
-        <v>6.1295999999999999</v>
+        <v>14.6386631611194</v>
       </c>
       <c r="G28">
-        <v>2.9</v>
+        <v>7.28177566987722</v>
       </c>
       <c r="H28">
-        <v>4.6043000000000003</v>
+        <v>6.70873672896467</v>
       </c>
       <c r="I28">
-        <v>4.2861000000000002</v>
+        <v>4.6274581441724703</v>
       </c>
       <c r="J28">
-        <v>3.6126999999999998</v>
+        <v>10.7257275550595</v>
       </c>
       <c r="L28">
-        <v>4.2537000000000003</v>
+        <v>3.89433974355451</v>
       </c>
       <c r="M28">
-        <v>4.2229999999999999</v>
+        <v>6.7570838097012702</v>
       </c>
       <c r="N28">
-        <v>3.4451999999999998</v>
+        <v>5.0053284665109903</v>
       </c>
       <c r="O28">
-        <v>4.1151</v>
+        <v>6.6723951221272797</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
@@ -1353,62 +1372,62 @@
         <v>6</v>
       </c>
       <c r="B29">
-        <v>21.332999999999998</v>
+        <v>23.885769838689001</v>
       </c>
       <c r="C29">
-        <v>10.309799999999999</v>
+        <v>26.964566445151402</v>
       </c>
       <c r="D29">
-        <v>17.6297</v>
+        <v>16.492176548647802</v>
       </c>
       <c r="E29">
-        <v>28.0839</v>
+        <v>79.198623030126498</v>
       </c>
       <c r="G29">
-        <v>14.8338</v>
+        <v>40.091052094092099</v>
       </c>
       <c r="H29">
-        <v>19.241299999999999</v>
+        <v>23.742891465465</v>
       </c>
       <c r="I29">
-        <v>20.048400000000001</v>
+        <v>20.585861268099599</v>
       </c>
       <c r="J29">
-        <v>15.324299999999999</v>
+        <v>57.151526954769203</v>
       </c>
       <c r="L29">
-        <v>19.8002</v>
+        <v>15.4462622801131</v>
       </c>
       <c r="M29">
-        <v>17.828800000000001</v>
+        <v>23.4629298168453</v>
       </c>
       <c r="N29">
-        <v>12.6289</v>
+        <v>20.4277010689643</v>
       </c>
       <c r="O29">
-        <v>19.4252</v>
+        <v>32.4053253287559</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="L31" s="3" t="s">
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="L31" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
@@ -1454,40 +1473,40 @@
         <v>1</v>
       </c>
       <c r="B33">
-        <v>9.1072000000000006</v>
+        <v>11.8848054465919</v>
       </c>
       <c r="C33">
-        <v>6.0353000000000003</v>
+        <v>10.9696967097089</v>
       </c>
       <c r="D33">
-        <v>6.7004000000000001</v>
+        <v>8.3111178574976901</v>
       </c>
       <c r="E33">
-        <v>9.4867000000000008</v>
+        <v>13.751826357299599</v>
       </c>
       <c r="G33">
-        <v>5.1012000000000004</v>
+        <v>8.7913964931890707</v>
       </c>
       <c r="H33">
-        <v>8.0045999999999999</v>
+        <v>10.5179271839494</v>
       </c>
       <c r="I33">
-        <v>7.6547999999999998</v>
+        <v>7.8614252552878199</v>
       </c>
       <c r="J33">
-        <v>5.4198000000000004</v>
+        <v>6.6917790585969401</v>
       </c>
       <c r="L33">
-        <v>5.8639000000000001</v>
+        <v>6.1375835714284701</v>
       </c>
       <c r="M33">
-        <v>7.5293999999999999</v>
+        <v>10.3321840816005</v>
       </c>
       <c r="N33">
-        <v>7.1844000000000001</v>
+        <v>8.2044111226557703</v>
       </c>
       <c r="O33">
-        <v>5.7424999999999997</v>
+        <v>6.4287391551487501</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -1495,40 +1514,40 @@
         <v>3</v>
       </c>
       <c r="B34">
-        <v>7.242</v>
+        <v>10.498718975587099</v>
       </c>
       <c r="C34">
-        <v>5.3532000000000002</v>
+        <v>8.7436668745418409</v>
       </c>
       <c r="D34">
-        <v>5.3358999999999996</v>
+        <v>6.99091755966327</v>
       </c>
       <c r="E34">
-        <v>7.8438999999999997</v>
+        <v>11.749288439232</v>
       </c>
       <c r="G34">
-        <v>4.0896999999999997</v>
+        <v>5.3951274349128697</v>
       </c>
       <c r="H34">
-        <v>6.6719999999999997</v>
+        <v>8.2564421476181593</v>
       </c>
       <c r="I34">
-        <v>6.3747999999999996</v>
+        <v>6.4468323446484996</v>
       </c>
       <c r="J34">
-        <v>3.8736000000000002</v>
+        <v>4.8651259145037002</v>
       </c>
       <c r="L34">
-        <v>4.6543000000000001</v>
+        <v>5.0145476378095397</v>
       </c>
       <c r="M34">
-        <v>6.3353000000000002</v>
+        <v>8.0194773179796996</v>
       </c>
       <c r="N34">
-        <v>6.3128000000000002</v>
+        <v>6.6689783119157902</v>
       </c>
       <c r="O34">
-        <v>4.0186000000000002</v>
+        <v>5.0492830973721903</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
@@ -1536,40 +1555,40 @@
         <v>5</v>
       </c>
       <c r="B35">
-        <v>5.5221</v>
+        <v>5.5700538933646104</v>
       </c>
       <c r="C35">
-        <v>2.7871999999999999</v>
+        <v>6.6243894428119603</v>
       </c>
       <c r="D35">
-        <v>4.0525000000000002</v>
+        <v>4.4946358823834398</v>
       </c>
       <c r="E35">
-        <v>5.3357999999999999</v>
+        <v>7.1461142821150601</v>
       </c>
       <c r="G35">
-        <v>3.0491000000000001</v>
+        <v>6.9412716602584803</v>
       </c>
       <c r="H35">
-        <v>4.4225000000000003</v>
+        <v>6.5159769267467604</v>
       </c>
       <c r="I35">
-        <v>4.2375999999999996</v>
+        <v>4.4989287352069898</v>
       </c>
       <c r="J35">
-        <v>3.7907999999999999</v>
+        <v>4.5946117142911103</v>
       </c>
       <c r="L35">
-        <v>3.5669</v>
+        <v>3.5389608763600999</v>
       </c>
       <c r="M35">
-        <v>4.0689000000000002</v>
+        <v>6.5147533677407097</v>
       </c>
       <c r="N35">
-        <v>3.4298000000000002</v>
+        <v>4.7788168143123597</v>
       </c>
       <c r="O35">
-        <v>4.1020000000000003</v>
+        <v>3.9791239397050902</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
@@ -1577,65 +1596,65 @@
         <v>7</v>
       </c>
       <c r="B36">
-        <v>20.974299999999999</v>
+        <v>23.646133015944599</v>
       </c>
       <c r="C36">
-        <v>10.7125</v>
+        <v>24.770577583177001</v>
       </c>
       <c r="D36">
-        <v>16.854399999999998</v>
+        <v>15.779669712282001</v>
       </c>
       <c r="E36">
-        <v>22.290800000000001</v>
+        <v>27.1001924208263</v>
       </c>
       <c r="G36">
-        <v>14.8813</v>
+        <v>38.999324312408802</v>
       </c>
       <c r="H36">
-        <v>18.823499999999999</v>
+        <v>23.555766493174399</v>
       </c>
       <c r="I36">
-        <v>19.4801</v>
+        <v>20.5588648541409</v>
       </c>
       <c r="J36">
-        <v>16.401</v>
+        <v>19.832559888211801</v>
       </c>
       <c r="L36">
-        <v>14.622199999999999</v>
+        <v>15.858355873931099</v>
       </c>
       <c r="M36">
-        <v>17.456800000000001</v>
+        <v>23.984539763698201</v>
       </c>
       <c r="N36">
-        <v>12.3162</v>
+        <v>20.599438904588698</v>
       </c>
       <c r="O36">
-        <v>19.483000000000001</v>
+        <v>15.458388645687</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
+      <c r="B38" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="L38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
+      <c r="G38" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="L38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
@@ -1681,40 +1700,40 @@
         <v>1</v>
       </c>
       <c r="B40">
-        <v>9.1072000000000006</v>
+        <v>11.8333459501627</v>
       </c>
       <c r="C40">
-        <v>6.0353000000000003</v>
+        <v>10.897677994417901</v>
       </c>
       <c r="D40">
-        <v>6.7004000000000001</v>
+        <v>8.3061155521881496</v>
       </c>
       <c r="E40">
-        <v>9.4867000000000008</v>
+        <v>13.709044634649899</v>
       </c>
       <c r="G40">
-        <v>5.1334999999999997</v>
+        <v>8.8538166722898595</v>
       </c>
       <c r="H40">
-        <v>8.0663</v>
+        <v>10.5782874124041</v>
       </c>
       <c r="I40">
-        <v>7.6698000000000004</v>
+        <v>7.8281250900161696</v>
       </c>
       <c r="J40">
-        <v>5.5716000000000001</v>
+        <v>6.7097059514052804</v>
       </c>
       <c r="L40">
-        <v>5.9287000000000001</v>
+        <v>6.2050820909798201</v>
       </c>
       <c r="M40">
-        <v>7.6289999999999996</v>
+        <v>10.398030606243299</v>
       </c>
       <c r="N40">
-        <v>7.1372</v>
+        <v>8.2181373579700292</v>
       </c>
       <c r="O40">
-        <v>5.7450000000000001</v>
+        <v>6.4787860801521102</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
@@ -1722,40 +1741,40 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>7.242</v>
+        <v>10.447325143556601</v>
       </c>
       <c r="C41">
-        <v>5.3532000000000002</v>
+        <v>8.6530975974968101</v>
       </c>
       <c r="D41">
-        <v>5.3358999999999996</v>
+        <v>7.0775608285539002</v>
       </c>
       <c r="E41">
-        <v>7.8438999999999997</v>
+        <v>11.7145409015843</v>
       </c>
       <c r="G41">
-        <v>4.1433</v>
+        <v>5.4688208442299597</v>
       </c>
       <c r="H41">
-        <v>6.7411000000000003</v>
+        <v>8.2626574372606392</v>
       </c>
       <c r="I41">
-        <v>6.4127000000000001</v>
+        <v>6.4676951358004997</v>
       </c>
       <c r="J41">
-        <v>3.9232</v>
+        <v>4.9139828948411397</v>
       </c>
       <c r="L41">
-        <v>4.7436999999999996</v>
+        <v>5.1118037820938902</v>
       </c>
       <c r="M41">
-        <v>6.4145000000000003</v>
+        <v>8.0384350611792001</v>
       </c>
       <c r="N41">
-        <v>6.2775999999999996</v>
+        <v>6.7407681490252198</v>
       </c>
       <c r="O41">
-        <v>3.9719000000000002</v>
+        <v>5.0644103121523303</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -1763,40 +1782,40 @@
         <v>5</v>
       </c>
       <c r="B42">
-        <v>5.5221</v>
+        <v>5.5571101951502904</v>
       </c>
       <c r="C42">
-        <v>2.7871999999999999</v>
+        <v>6.6244462137008604</v>
       </c>
       <c r="D42">
-        <v>4.0525000000000002</v>
+        <v>4.3473771730114796</v>
       </c>
       <c r="E42">
-        <v>5.3357999999999999</v>
+        <v>7.1209154088453799</v>
       </c>
       <c r="G42">
-        <v>3.0308999999999999</v>
+        <v>6.9629065942488202</v>
       </c>
       <c r="H42">
-        <v>4.4298000000000002</v>
+        <v>6.6051992137944104</v>
       </c>
       <c r="I42">
-        <v>4.2073999999999998</v>
+        <v>4.4100410491607898</v>
       </c>
       <c r="J42">
-        <v>3.9561999999999999</v>
+        <v>4.5686897534776998</v>
       </c>
       <c r="L42">
-        <v>3.5562</v>
+        <v>3.5174572988408901</v>
       </c>
       <c r="M42">
-        <v>4.1299000000000001</v>
+        <v>6.5956502526724199</v>
       </c>
       <c r="N42">
-        <v>3.3957000000000002</v>
+        <v>4.70104524500133</v>
       </c>
       <c r="O42">
-        <v>4.1506999999999996</v>
+        <v>4.04059615187386</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
@@ -1804,49 +1823,745 @@
         <v>7</v>
       </c>
       <c r="B43">
-        <v>20.974299999999999</v>
+        <v>23.900900451929001</v>
       </c>
       <c r="C43">
-        <v>10.7125</v>
+        <v>24.499894341494301</v>
       </c>
       <c r="D43">
-        <v>16.854399999999998</v>
+        <v>15.6227049333576</v>
       </c>
       <c r="E43">
-        <v>22.290800000000001</v>
+        <v>26.426433898962301</v>
       </c>
       <c r="G43">
-        <v>14.5664</v>
+        <v>38.999324312408802</v>
       </c>
       <c r="H43">
-        <v>18.603300000000001</v>
+        <v>23.551237930492402</v>
       </c>
       <c r="I43">
-        <v>19.517900000000001</v>
+        <v>20.5344095901667</v>
       </c>
       <c r="J43">
-        <v>16.264099999999999</v>
+        <v>19.832559888211801</v>
       </c>
       <c r="L43">
-        <v>14.622199999999999</v>
+        <v>15.858355873931099</v>
       </c>
       <c r="M43">
-        <v>17.232099999999999</v>
+        <v>23.9764608356348</v>
       </c>
       <c r="N43">
-        <v>12.384399999999999</v>
+        <v>20.645079818535098</v>
       </c>
       <c r="O43">
-        <v>19.345099999999999</v>
-      </c>
-      <c r="Q43" s="3" t="s">
+        <v>15.458388645687</v>
+      </c>
+      <c r="Q43" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+    </row>
+    <row r="45" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B47" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="L47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J48" t="s">
+        <v>14</v>
+      </c>
+      <c r="L48" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" t="s">
+        <v>10</v>
+      </c>
+      <c r="N48" t="s">
+        <v>12</v>
+      </c>
+      <c r="O48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49">
+        <v>12.9226334079941</v>
+      </c>
+      <c r="C49">
+        <v>11.279463788733899</v>
+      </c>
+      <c r="D49">
+        <v>8.3753137072889494</v>
+      </c>
+      <c r="E49">
+        <v>20.414639302315098</v>
+      </c>
+      <c r="G49">
+        <v>9.2443529216786295</v>
+      </c>
+      <c r="H49">
+        <v>10.574718446765401</v>
+      </c>
+      <c r="I49">
+        <v>7.9462428018564504</v>
+      </c>
+      <c r="J49">
+        <v>12.2249696301109</v>
+      </c>
+      <c r="L49">
+        <v>6.5592623721608803</v>
+      </c>
+      <c r="M49">
+        <v>10.323050458630499</v>
+      </c>
+      <c r="N49">
+        <v>8.3853775250676108</v>
+      </c>
+      <c r="O49">
+        <v>8.68679227273614</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50">
+        <v>11.3374353772259</v>
+      </c>
+      <c r="C50">
+        <v>8.6579712106884497</v>
+      </c>
+      <c r="D50">
+        <v>6.89697399140291</v>
+      </c>
+      <c r="E50">
+        <v>14.229091281558199</v>
+      </c>
+      <c r="G50">
+        <v>5.6950683959134496</v>
+      </c>
+      <c r="H50">
+        <v>8.1741985374592403</v>
+      </c>
+      <c r="I50">
+        <v>6.4598301672712202</v>
+      </c>
+      <c r="J50">
+        <v>5.8658887537840796</v>
+      </c>
+      <c r="L50">
+        <v>5.2780716960474603</v>
+      </c>
+      <c r="M50">
+        <v>7.8043058089816197</v>
+      </c>
+      <c r="N50">
+        <v>6.72764767063821</v>
+      </c>
+      <c r="O50">
+        <v>5.5623289478311397</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>6.2013718856903397</v>
+      </c>
+      <c r="C51">
+        <v>7.2295115932025702</v>
+      </c>
+      <c r="D51">
+        <v>4.7515923075758497</v>
+      </c>
+      <c r="E51">
+        <v>14.6386631611194</v>
+      </c>
+      <c r="G51">
+        <v>7.28177566987722</v>
+      </c>
+      <c r="H51">
+        <v>6.70873672896467</v>
+      </c>
+      <c r="I51">
+        <v>4.6274581441724703</v>
+      </c>
+      <c r="J51">
+        <v>10.7257275550595</v>
+      </c>
+      <c r="L51">
+        <v>3.89433974355451</v>
+      </c>
+      <c r="M51">
+        <v>6.7570838097012702</v>
+      </c>
+      <c r="N51">
+        <v>5.0053284665109903</v>
+      </c>
+      <c r="O51">
+        <v>6.6723951221272797</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52">
+        <v>23.885769838689001</v>
+      </c>
+      <c r="C52">
+        <v>26.964566445151402</v>
+      </c>
+      <c r="D52">
+        <v>16.492176548647802</v>
+      </c>
+      <c r="E52">
+        <v>79.198623030126498</v>
+      </c>
+      <c r="G52">
+        <v>40.091052094092099</v>
+      </c>
+      <c r="H52">
+        <v>23.742891465465</v>
+      </c>
+      <c r="I52">
+        <v>20.585861268099599</v>
+      </c>
+      <c r="J52">
+        <v>57.151526954769203</v>
+      </c>
+      <c r="L52">
+        <v>15.4462622801131</v>
+      </c>
+      <c r="M52">
+        <v>23.4629298168453</v>
+      </c>
+      <c r="N52">
+        <v>20.4277010689643</v>
+      </c>
+      <c r="O52">
+        <v>32.4053253287559</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="L54" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" t="s">
+        <v>8</v>
+      </c>
+      <c r="M55" t="s">
+        <v>10</v>
+      </c>
+      <c r="N55" t="s">
+        <v>12</v>
+      </c>
+      <c r="O55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56">
+        <v>11.8848054465919</v>
+      </c>
+      <c r="C56">
+        <v>10.9696967097089</v>
+      </c>
+      <c r="D56">
+        <v>8.3111178574976901</v>
+      </c>
+      <c r="E56">
+        <v>13.751826357299599</v>
+      </c>
+      <c r="G56">
+        <v>8.7913964931890707</v>
+      </c>
+      <c r="H56">
+        <v>10.5179271839494</v>
+      </c>
+      <c r="I56">
+        <v>7.8614252552878199</v>
+      </c>
+      <c r="J56">
+        <v>6.6917790585969401</v>
+      </c>
+      <c r="L56">
+        <v>6.1375835714284701</v>
+      </c>
+      <c r="M56">
+        <v>10.3321840816005</v>
+      </c>
+      <c r="N56">
+        <v>8.2044111226557703</v>
+      </c>
+      <c r="O56">
+        <v>6.4287391551487501</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57">
+        <v>10.498718975587099</v>
+      </c>
+      <c r="C57">
+        <v>8.7436668745418409</v>
+      </c>
+      <c r="D57">
+        <v>6.99091755966327</v>
+      </c>
+      <c r="E57">
+        <v>11.749288439232</v>
+      </c>
+      <c r="G57">
+        <v>5.3951274349128697</v>
+      </c>
+      <c r="H57">
+        <v>8.2564421476181593</v>
+      </c>
+      <c r="I57">
+        <v>6.4468323446484996</v>
+      </c>
+      <c r="J57">
+        <v>4.8651259145037002</v>
+      </c>
+      <c r="L57">
+        <v>5.0145476378095397</v>
+      </c>
+      <c r="M57">
+        <v>8.0194773179796996</v>
+      </c>
+      <c r="N57">
+        <v>6.6689783119157902</v>
+      </c>
+      <c r="O57">
+        <v>5.0492830973721903</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58">
+        <v>5.5700538933646104</v>
+      </c>
+      <c r="C58">
+        <v>6.6243894428119603</v>
+      </c>
+      <c r="D58">
+        <v>4.4946358823834398</v>
+      </c>
+      <c r="E58">
+        <v>7.1461142821150601</v>
+      </c>
+      <c r="G58">
+        <v>6.9412716602584803</v>
+      </c>
+      <c r="H58">
+        <v>6.5159769267467604</v>
+      </c>
+      <c r="I58">
+        <v>4.4989287352069898</v>
+      </c>
+      <c r="J58">
+        <v>4.5946117142911103</v>
+      </c>
+      <c r="L58">
+        <v>3.5389608763600999</v>
+      </c>
+      <c r="M58">
+        <v>6.5147533677407097</v>
+      </c>
+      <c r="N58">
+        <v>4.7788168143123597</v>
+      </c>
+      <c r="O58">
+        <v>3.9791239397050902</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59">
+        <v>23.646133015944599</v>
+      </c>
+      <c r="C59">
+        <v>24.770577583177001</v>
+      </c>
+      <c r="D59">
+        <v>15.779669712282001</v>
+      </c>
+      <c r="E59">
+        <v>27.1001924208263</v>
+      </c>
+      <c r="G59">
+        <v>38.999324312408802</v>
+      </c>
+      <c r="H59">
+        <v>23.555766493174399</v>
+      </c>
+      <c r="I59">
+        <v>20.5588648541409</v>
+      </c>
+      <c r="J59">
+        <v>19.832559888211801</v>
+      </c>
+      <c r="L59">
+        <v>15.858355873931099</v>
+      </c>
+      <c r="M59">
+        <v>23.984539763698201</v>
+      </c>
+      <c r="N59">
+        <v>20.599438904588698</v>
+      </c>
+      <c r="O59">
+        <v>15.458388645687</v>
+      </c>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B61" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="L61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B62" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L62" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" t="s">
+        <v>10</v>
+      </c>
+      <c r="N62" t="s">
+        <v>12</v>
+      </c>
+      <c r="O62" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63">
+        <v>11.8333459501627</v>
+      </c>
+      <c r="C63">
+        <v>10.897677994417901</v>
+      </c>
+      <c r="D63">
+        <v>8.3061155521881496</v>
+      </c>
+      <c r="E63">
+        <v>13.709044634649899</v>
+      </c>
+      <c r="G63">
+        <v>8.8538166722898595</v>
+      </c>
+      <c r="H63">
+        <v>10.5782874124041</v>
+      </c>
+      <c r="I63">
+        <v>7.8281250900161696</v>
+      </c>
+      <c r="J63">
+        <v>6.7097059514052804</v>
+      </c>
+      <c r="L63">
+        <v>6.2050820909798201</v>
+      </c>
+      <c r="M63">
+        <v>10.398030606243299</v>
+      </c>
+      <c r="N63">
+        <v>8.2181373579700292</v>
+      </c>
+      <c r="O63">
+        <v>6.4787860801521102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64">
+        <v>10.447325143556601</v>
+      </c>
+      <c r="C64">
+        <v>8.6530975974968101</v>
+      </c>
+      <c r="D64">
+        <v>7.0775608285539002</v>
+      </c>
+      <c r="E64">
+        <v>11.7145409015843</v>
+      </c>
+      <c r="G64">
+        <v>5.4688208442299597</v>
+      </c>
+      <c r="H64">
+        <v>8.2626574372606392</v>
+      </c>
+      <c r="I64">
+        <v>6.4676951358004997</v>
+      </c>
+      <c r="J64">
+        <v>4.9139828948411397</v>
+      </c>
+      <c r="L64">
+        <v>5.1118037820938902</v>
+      </c>
+      <c r="M64">
+        <v>8.0384350611792001</v>
+      </c>
+      <c r="N64">
+        <v>6.7407681490252198</v>
+      </c>
+      <c r="O64">
+        <v>5.0644103121523303</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>5.5571101951502904</v>
+      </c>
+      <c r="C65">
+        <v>6.6244462137008604</v>
+      </c>
+      <c r="D65">
+        <v>4.3473771730114796</v>
+      </c>
+      <c r="E65">
+        <v>7.1209154088453799</v>
+      </c>
+      <c r="G65">
+        <v>6.9629065942488202</v>
+      </c>
+      <c r="H65">
+        <v>6.6051992137944104</v>
+      </c>
+      <c r="I65">
+        <v>4.4100410491607898</v>
+      </c>
+      <c r="J65">
+        <v>4.5686897534776998</v>
+      </c>
+      <c r="L65">
+        <v>3.5174572988408901</v>
+      </c>
+      <c r="M65">
+        <v>6.5956502526724199</v>
+      </c>
+      <c r="N65">
+        <v>4.70104524500133</v>
+      </c>
+      <c r="O65">
+        <v>4.04059615187386</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66">
+        <v>23.900900451929001</v>
+      </c>
+      <c r="C66">
+        <v>24.499894341494301</v>
+      </c>
+      <c r="D66">
+        <v>15.6227049333576</v>
+      </c>
+      <c r="E66">
+        <v>26.426433898962301</v>
+      </c>
+      <c r="G66">
+        <v>38.999324312408802</v>
+      </c>
+      <c r="H66">
+        <v>23.551237930492402</v>
+      </c>
+      <c r="I66">
+        <v>20.5344095901667</v>
+      </c>
+      <c r="J66">
+        <v>19.832559888211801</v>
+      </c>
+      <c r="L66">
+        <v>15.858355873931099</v>
+      </c>
+      <c r="M66">
+        <v>23.9764608356348</v>
+      </c>
+      <c r="N66">
+        <v>20.645079818535098</v>
+      </c>
+      <c r="O66">
+        <v>15.458388645687</v>
+      </c>
+      <c r="Q66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R66" s="5"/>
+      <c r="S66" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="30">
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="G61:J61"/>
+    <mergeCell ref="L61:O61"/>
+    <mergeCell ref="Q66:S66"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="L47:O47"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="L54:O54"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G8:J8"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="L38:O38"/>
@@ -1861,12 +2576,6 @@
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="L31:O31"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="L8:O8"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="G8:J8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
